--- a/RAMON FRANCO/Julio/PRORRATEO-RAMON-FRANCO-Julio.xlsx
+++ b/RAMON FRANCO/Julio/PRORRATEO-RAMON-FRANCO-Julio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A0122B-C54F-4C66-BA7F-D6A03062D606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1331ED7-09F1-4CDC-8341-129737E619CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -277,7 +277,7 @@
     <t>GISELA</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 14/07 LIQUIDACION: JUNIO</t>
+    <t>EXPENSAS - VENCIMIENTO 14/08 LIQUIDACION: JULIO</t>
   </si>
 </sst>
 </file>
@@ -673,7 +673,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -850,7 +850,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1310,7 +1309,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="25"/>
       <c r="C7" s="26">
-        <v>1414065.58</v>
+        <v>1251619.77</v>
       </c>
       <c r="D7" s="26"/>
       <c r="F7" s="4"/>
@@ -1436,35 +1435,32 @@
         <v>7.99</v>
       </c>
       <c r="F12" s="58">
-        <v>261166.1401829088</v>
+        <v>112983.839842</v>
       </c>
       <c r="G12" s="44">
         <v>0</v>
       </c>
-      <c r="H12" s="88">
-        <f>F12</f>
-        <v>261166.1401829088</v>
-      </c>
+      <c r="H12" s="69"/>
       <c r="I12" s="44" t="e">
         <f>C9*E12/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J12" s="44">
         <f t="shared" ref="J12:J19" si="0">F12-G12-H12</f>
-        <v>0</v>
+        <v>112983.839842</v>
       </c>
       <c r="K12" s="44"/>
       <c r="L12" s="45">
         <f>(J12+K12)*8%</f>
-        <v>0</v>
+        <v>9038.7071873599998</v>
       </c>
       <c r="M12" s="45">
         <f>J12+L12+K12</f>
-        <v>0</v>
+        <v>122022.54702935999</v>
       </c>
       <c r="N12" s="44">
         <f>C7*E12/100</f>
-        <v>112983.839842</v>
+        <v>100004.41962300001</v>
       </c>
       <c r="O12" s="44">
         <f t="shared" ref="O12:O29" si="1">C$10*E12/100</f>
@@ -1472,7 +1468,7 @@
       </c>
       <c r="P12" s="45">
         <f>N12+M12+O12</f>
-        <v>112983.839842</v>
+        <v>222026.96665235999</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1492,14 +1488,14 @@
         <v>6.05</v>
       </c>
       <c r="F13" s="58">
-        <v>211506.99285835007</v>
+        <v>85550.96759</v>
       </c>
       <c r="G13" s="44">
         <v>0</v>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="69">
         <f>F13</f>
-        <v>211506.99285835007</v>
+        <v>85550.96759</v>
       </c>
       <c r="I13" s="44" t="e">
         <f>C9*E13/100</f>
@@ -1520,7 +1516,7 @@
       </c>
       <c r="N13" s="44">
         <f>C7*E13/100</f>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="O13" s="44">
         <f t="shared" si="1"/>
@@ -1528,7 +1524,7 @@
       </c>
       <c r="P13" s="45">
         <f t="shared" ref="P13:P29" si="4">N13+M13+O13</f>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1548,14 +1544,14 @@
         <v>6.02</v>
       </c>
       <c r="F14" s="58">
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="G14" s="44">
         <v>0</v>
       </c>
-      <c r="H14" s="88">
+      <c r="H14" s="69">
         <f t="shared" ref="H14:H29" si="5">F14</f>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="I14" s="44" t="e">
         <f>C9*E14/100</f>
@@ -1576,7 +1572,7 @@
       </c>
       <c r="N14" s="44">
         <f>C7*E14/100</f>
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
       <c r="O14" s="44">
         <f t="shared" si="1"/>
@@ -1584,7 +1580,7 @@
       </c>
       <c r="P14" s="45">
         <f t="shared" si="4"/>
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1602,33 +1598,30 @@
         <v>7.63</v>
       </c>
       <c r="F15" s="60">
-        <v>60631.215120000001</v>
+        <v>107893.20375400002</v>
       </c>
       <c r="G15" s="46"/>
-      <c r="H15" s="88">
-        <f t="shared" si="5"/>
-        <v>60631.215120000001</v>
-      </c>
+      <c r="H15" s="69"/>
       <c r="I15" s="44" t="e">
         <f>C9*E15/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J15" s="44">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>107893.20375400002</v>
       </c>
       <c r="K15" s="48"/>
       <c r="L15" s="45">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8631.4563003200019</v>
       </c>
       <c r="M15" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>116524.66005432002</v>
       </c>
       <c r="N15" s="50">
         <f>C7*E15/100</f>
-        <v>107893.20375400002</v>
+        <v>95498.588451000003</v>
       </c>
       <c r="O15" s="44">
         <f t="shared" si="1"/>
@@ -1636,7 +1629,7 @@
       </c>
       <c r="P15" s="45">
         <f t="shared" si="4"/>
-        <v>107893.20375400002</v>
+        <v>212023.24850532002</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1656,14 +1649,14 @@
         <v>6.05</v>
       </c>
       <c r="F16" s="58">
-        <v>146861.41881599999</v>
+        <v>85550.96759</v>
       </c>
       <c r="G16" s="46">
         <v>0</v>
       </c>
-      <c r="H16" s="88">
+      <c r="H16" s="69">
         <f>F16</f>
-        <v>146861.41881599999</v>
+        <v>85550.96759</v>
       </c>
       <c r="I16" s="44" t="e">
         <f>C9*E16/100</f>
@@ -1684,7 +1677,7 @@
       </c>
       <c r="N16" s="44">
         <f>C7*E16/100</f>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="O16" s="44">
         <f t="shared" si="1"/>
@@ -1692,7 +1685,7 @@
       </c>
       <c r="P16" s="45">
         <f t="shared" si="4"/>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1712,14 +1705,14 @@
         <v>6.02</v>
       </c>
       <c r="F17" s="58">
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="G17" s="44">
         <v>0</v>
       </c>
-      <c r="H17" s="88">
+      <c r="H17" s="69">
         <f>F17</f>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="I17" s="44" t="e">
         <f>C9*E17/100</f>
@@ -1740,7 +1733,7 @@
       </c>
       <c r="N17" s="44">
         <f>C7*E17/100</f>
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
       <c r="O17" s="44">
         <f t="shared" si="1"/>
@@ -1748,7 +1741,7 @@
       </c>
       <c r="P17" s="45">
         <f t="shared" si="4"/>
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1766,14 +1759,14 @@
         <v>7.63</v>
       </c>
       <c r="F18" s="58">
-        <v>60631.215120000001</v>
+        <v>107893.20375400002</v>
       </c>
       <c r="G18" s="44">
         <v>0</v>
       </c>
-      <c r="H18" s="88">
-        <f t="shared" si="5"/>
-        <v>60631.215120000001</v>
+      <c r="H18" s="69">
+        <f>F18</f>
+        <v>107893.20375400002</v>
       </c>
       <c r="I18" s="44" t="e">
         <f>C9*E18/100</f>
@@ -1794,7 +1787,7 @@
       </c>
       <c r="N18" s="44">
         <f>C7*E18/100</f>
-        <v>107893.20375400002</v>
+        <v>95498.588451000003</v>
       </c>
       <c r="O18" s="44">
         <f t="shared" si="1"/>
@@ -1802,7 +1795,7 @@
       </c>
       <c r="P18" s="45">
         <f t="shared" si="4"/>
-        <v>107893.20375400002</v>
+        <v>95498.588451000003</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1822,14 +1815,14 @@
         <v>6.05</v>
       </c>
       <c r="F19" s="58">
-        <v>188076.42732298671</v>
+        <v>85550.96759</v>
       </c>
       <c r="G19" s="44">
         <v>0</v>
       </c>
-      <c r="H19" s="88">
+      <c r="H19" s="69">
         <f>F19</f>
-        <v>188076.42732298671</v>
+        <v>85550.96759</v>
       </c>
       <c r="I19" s="44" t="e">
         <f>C9*E19/100</f>
@@ -1850,7 +1843,7 @@
       </c>
       <c r="N19" s="44">
         <f>C7*E19/100</f>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="O19" s="44">
         <f t="shared" si="1"/>
@@ -1858,7 +1851,7 @@
       </c>
       <c r="P19" s="45">
         <f>N19+M19+O19</f>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1876,14 +1869,14 @@
         <v>6.02</v>
       </c>
       <c r="F20" s="58">
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="G20" s="44">
         <v>0</v>
       </c>
-      <c r="H20" s="88">
+      <c r="H20" s="69">
         <f t="shared" si="5"/>
-        <v>47837.472479999997</v>
+        <v>85126.747916000008</v>
       </c>
       <c r="I20" s="44" t="e">
         <f>C9*E20/100</f>
@@ -1904,7 +1897,7 @@
       </c>
       <c r="N20" s="44">
         <f>C7*E20/100</f>
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
       <c r="O20" s="44">
         <f t="shared" si="1"/>
@@ -1912,7 +1905,7 @@
       </c>
       <c r="P20" s="45">
         <f t="shared" si="4"/>
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1930,14 +1923,14 @@
         <v>21.2</v>
       </c>
       <c r="F21" s="58">
-        <v>168464.1888</v>
+        <v>299781.90295999998</v>
       </c>
       <c r="G21" s="44">
         <v>0</v>
       </c>
-      <c r="H21" s="88">
+      <c r="H21" s="69">
         <f>F21</f>
-        <v>168464.1888</v>
+        <v>299781.90295999998</v>
       </c>
       <c r="I21" s="44" t="e">
         <f>C9*E21/100</f>
@@ -1958,7 +1951,7 @@
       </c>
       <c r="N21" s="44">
         <f>C7*E21/100</f>
-        <v>299781.90295999998</v>
+        <v>265343.39123999997</v>
       </c>
       <c r="O21" s="44">
         <f t="shared" si="1"/>
@@ -1966,7 +1959,7 @@
       </c>
       <c r="P21" s="45">
         <f t="shared" si="4"/>
-        <v>299781.90295999998</v>
+        <v>265343.39123999997</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1986,14 +1979,14 @@
         <v>6.81</v>
       </c>
       <c r="F22" s="58">
-        <v>54115.147440000001</v>
+        <v>96297.865997999994</v>
       </c>
       <c r="G22" s="44">
         <v>0</v>
       </c>
-      <c r="H22" s="88">
+      <c r="H22" s="69">
         <f>F22</f>
-        <v>54115.147440000001</v>
+        <v>96297.865997999994</v>
       </c>
       <c r="I22" s="44" t="e">
         <f>C9*E22/100</f>
@@ -2014,7 +2007,7 @@
       </c>
       <c r="N22" s="44">
         <f>C7*E22/100</f>
-        <v>96297.865997999994</v>
+        <v>85235.306337000002</v>
       </c>
       <c r="O22" s="44">
         <f t="shared" si="1"/>
@@ -2022,7 +2015,7 @@
       </c>
       <c r="P22" s="45">
         <f t="shared" si="4"/>
-        <v>96297.865997999994</v>
+        <v>85235.306337000002</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2042,14 +2035,14 @@
         <v>6.52</v>
       </c>
       <c r="F23" s="69">
-        <v>167199.87925714575</v>
+        <v>92197.075815999997</v>
       </c>
       <c r="G23" s="44">
         <v>0</v>
       </c>
-      <c r="H23" s="88">
+      <c r="H23" s="69">
         <f>F23</f>
-        <v>167199.87925714575</v>
+        <v>92197.075815999997</v>
       </c>
       <c r="I23" s="44">
         <v>0</v>
@@ -2069,7 +2062,7 @@
       </c>
       <c r="N23" s="44">
         <f>C7*E23/100</f>
-        <v>92197.075815999997</v>
+        <v>81605.609003999998</v>
       </c>
       <c r="O23" s="44">
         <f t="shared" si="1"/>
@@ -2077,7 +2070,7 @@
       </c>
       <c r="P23" s="45">
         <f t="shared" si="4"/>
-        <v>92197.075815999997</v>
+        <v>81605.609003999998</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2095,32 +2088,32 @@
         <v>1.18</v>
       </c>
       <c r="F24" s="58">
-        <v>426707.01996165415</v>
+        <v>477529.55540258653</v>
       </c>
       <c r="G24" s="44">
         <v>0</v>
       </c>
-      <c r="H24" s="88"/>
+      <c r="H24" s="69"/>
       <c r="I24" s="44" t="e">
         <f>C9*E24/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J24" s="44">
         <f t="shared" si="7"/>
-        <v>426707.01996165415</v>
+        <v>477529.55540258653</v>
       </c>
       <c r="K24" s="44"/>
       <c r="L24" s="45">
         <f t="shared" si="2"/>
-        <v>34136.561596932333</v>
+        <v>38202.364432206923</v>
       </c>
       <c r="M24" s="45">
         <f t="shared" si="6"/>
-        <v>460843.58155858651</v>
+        <v>515731.91983479343</v>
       </c>
       <c r="N24" s="44">
         <f>C7*E24/100</f>
-        <v>16685.973844</v>
+        <v>14769.113286</v>
       </c>
       <c r="O24" s="44">
         <f t="shared" si="1"/>
@@ -2128,7 +2121,7 @@
       </c>
       <c r="P24" s="45">
         <f t="shared" si="4"/>
-        <v>477529.55540258653</v>
+        <v>530501.03312079341</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2146,12 +2139,12 @@
         <v>1.17</v>
       </c>
       <c r="F25" s="58">
-        <v>421093.78143863485</v>
+        <v>471325.85123972566</v>
       </c>
       <c r="G25" s="44">
         <v>0</v>
       </c>
-      <c r="H25" s="88">
+      <c r="H25" s="69">
         <v>0</v>
       </c>
       <c r="I25" s="44" t="e">
@@ -2160,20 +2153,20 @@
       </c>
       <c r="J25" s="44">
         <f t="shared" si="7"/>
-        <v>421093.78143863485</v>
+        <v>471325.85123972566</v>
       </c>
       <c r="K25" s="44"/>
       <c r="L25" s="45">
         <f t="shared" si="2"/>
-        <v>33687.50251509079</v>
+        <v>37706.068099178054</v>
       </c>
       <c r="M25" s="45">
         <f t="shared" si="6"/>
-        <v>454781.28395372565</v>
+        <v>509031.91933890374</v>
       </c>
       <c r="N25" s="44">
         <f>C7*E25/100</f>
-        <v>16544.567286000001</v>
+        <v>14643.951309</v>
       </c>
       <c r="O25" s="44">
         <f t="shared" si="1"/>
@@ -2181,7 +2174,7 @@
       </c>
       <c r="P25" s="45">
         <f t="shared" si="4"/>
-        <v>471325.85123972566</v>
+        <v>523675.87064790376</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2199,14 +2192,14 @@
         <v>1.06</v>
       </c>
       <c r="F26" s="58">
-        <v>8423.2094400000005</v>
+        <v>14989.095148000002</v>
       </c>
       <c r="G26" s="44">
         <v>0</v>
       </c>
-      <c r="H26" s="88">
+      <c r="H26" s="69">
         <f>F26</f>
-        <v>8423.2094400000005</v>
+        <v>14989.095148000002</v>
       </c>
       <c r="I26" s="44" t="e">
         <f>C9*E26/100</f>
@@ -2227,7 +2220,7 @@
       </c>
       <c r="N26" s="44">
         <f>C7*E26/100</f>
-        <v>14989.095148000002</v>
+        <v>13267.169562000001</v>
       </c>
       <c r="O26" s="44">
         <f t="shared" si="1"/>
@@ -2235,7 +2228,7 @@
       </c>
       <c r="P26" s="45">
         <f t="shared" si="4"/>
-        <v>14989.095148000002</v>
+        <v>13267.169562000001</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2253,32 +2246,32 @@
         <v>0.51</v>
       </c>
       <c r="F27" s="58">
-        <v>25173.480543237325</v>
+        <v>34399.093444696315</v>
       </c>
       <c r="G27" s="44">
         <v>0</v>
       </c>
-      <c r="H27" s="88"/>
+      <c r="H27" s="69"/>
       <c r="I27" s="44" t="e">
         <f>C9*E27/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J27" s="44">
         <f t="shared" si="7"/>
-        <v>25173.480543237325</v>
+        <v>34399.093444696315</v>
       </c>
       <c r="K27" s="44"/>
       <c r="L27" s="45">
         <f t="shared" si="2"/>
-        <v>2013.8784434589861</v>
+        <v>2751.9274755757051</v>
       </c>
       <c r="M27" s="45">
         <f t="shared" si="6"/>
-        <v>27187.358986696312</v>
+        <v>37151.020920272022</v>
       </c>
       <c r="N27" s="44">
         <f>C7*E27/100</f>
-        <v>7211.7344580000008</v>
+        <v>6383.2608270000001</v>
       </c>
       <c r="O27" s="44">
         <f t="shared" si="1"/>
@@ -2286,7 +2279,7 @@
       </c>
       <c r="P27" s="45">
         <f t="shared" si="4"/>
-        <v>34399.093444696315</v>
+        <v>43534.28174727202</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2304,14 +2297,14 @@
         <v>0.27</v>
       </c>
       <c r="F28" s="58">
-        <v>2145.5344800000003</v>
+        <v>3817.9770660000004</v>
       </c>
       <c r="G28" s="44">
         <v>0</v>
       </c>
-      <c r="H28" s="88">
+      <c r="H28" s="69">
         <f t="shared" si="5"/>
-        <v>2145.5344800000003</v>
+        <v>3817.9770660000004</v>
       </c>
       <c r="I28" s="44" t="e">
         <f>C9*E28/100</f>
@@ -2332,7 +2325,7 @@
       </c>
       <c r="N28" s="44">
         <f>C7*E28/100</f>
-        <v>3817.9770660000004</v>
+        <v>3379.3733790000006</v>
       </c>
       <c r="O28" s="44">
         <f t="shared" si="1"/>
@@ -2340,7 +2333,7 @@
       </c>
       <c r="P28" s="45">
         <f t="shared" si="4"/>
-        <v>3817.9770660000004</v>
+        <v>3379.3733790000006</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2356,14 +2349,14 @@
         <v>1.82</v>
       </c>
       <c r="F29" s="59">
-        <v>14462.491680000001</v>
+        <v>25735.993556000005</v>
       </c>
       <c r="G29" s="44">
         <v>0</v>
       </c>
-      <c r="H29" s="88">
+      <c r="H29" s="69">
         <f t="shared" si="5"/>
-        <v>14462.491680000001</v>
+        <v>25735.993556000005</v>
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="44">
@@ -2381,7 +2374,7 @@
       </c>
       <c r="N29" s="48">
         <f>C7*E29/100</f>
-        <v>25735.993556000005</v>
+        <v>22779.479813999998</v>
       </c>
       <c r="O29" s="44">
         <f t="shared" si="1"/>
@@ -2389,7 +2382,7 @@
       </c>
       <c r="P29" s="45">
         <f t="shared" si="4"/>
-        <v>25735.993556000005</v>
+        <v>22779.479813999998</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
@@ -2402,7 +2395,7 @@
       <c r="E30" s="42"/>
       <c r="F30" s="54">
         <f>SUM(F12:F29)</f>
-        <v>2360170.5599009171</v>
+        <v>2356877.8044990078</v>
       </c>
       <c r="G30" s="54">
         <f>SUM(G12:G29)</f>
@@ -2410,22 +2403,22 @@
       </c>
       <c r="H30" s="62">
         <f>SUM(H12:H29)</f>
-        <v>1487196.277957391</v>
+        <v>1152746.2608159999</v>
       </c>
       <c r="I30" s="54"/>
       <c r="J30" s="62">
         <f>SUM(J12:J29)</f>
-        <v>872974.28194352624</v>
+        <v>1204131.5436830085</v>
       </c>
       <c r="K30" s="54"/>
       <c r="L30" s="68">
         <f>L12+L13+L14+L15+L16+L17+L18+L19+L20+L21+L22+L23+L24+L25+L26+L27+L28+L29</f>
-        <v>69837.942555482121</v>
+        <v>96330.523494640685</v>
       </c>
       <c r="M30" s="55"/>
       <c r="N30" s="70">
         <f>SUM(N12:N29)</f>
-        <v>1414065.5799999994</v>
+        <v>1251619.77</v>
       </c>
       <c r="O30" s="56">
         <f>SUM(O12:O29)</f>
@@ -2433,7 +2426,7 @@
       </c>
       <c r="P30" s="57">
         <f>SUM(P16:P29) +P15+P14+P13+P12</f>
-        <v>2356877.8044990087</v>
+        <v>2552081.8371776491</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
